--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>133696982</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>133698127</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>133696761</v>
       </c>
       <c r="B7" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>133698174</v>
       </c>
       <c r="B8" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>133697616</v>
       </c>
       <c r="B10" t="n">
-        <v>96766</v>
+        <v>96773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>133696898</v>
       </c>
       <c r="B11" t="n">
-        <v>97796</v>
+        <v>97803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>134287731</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>134288280</v>
       </c>
       <c r="B13" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>134288382</v>
       </c>
       <c r="B14" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133698197</v>
+        <v>133698174</v>
       </c>
       <c r="B2" t="n">
-        <v>4776</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>325432</v>
+        <v>325446</v>
       </c>
       <c r="R2" t="n">
-        <v>6557678</v>
+        <v>6557657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,54 +777,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133696875</v>
+        <v>134288280</v>
       </c>
       <c r="B3" t="n">
-        <v>5181</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr Kuvetjärnen, Dls</t>
+          <t>Söder om Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325375</v>
+        <v>325587</v>
       </c>
       <c r="R3" t="n">
-        <v>6557928</v>
+        <v>6557366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,25 +868,45 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133696982</v>
+        <v>134288382</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,45 +914,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sydost Kuvetjärnen, Dls</t>
+          <t>Norr om Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>325668</v>
+        <v>325377</v>
       </c>
       <c r="R4" t="n">
-        <v>6557541</v>
+        <v>6557890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,63 +990,92 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Låga med markkontakt # Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133698127</v>
+        <v>133697489</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>96780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>535</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söder Lilla Lekarvall, Dls</t>
+          <t>SSO Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325663</v>
+        <v>325565</v>
       </c>
       <c r="R5" t="n">
-        <v>6557566</v>
+        <v>6557419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1112,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På hård kärnved av naturlig tallhögstubbe i exponerat läge.</t>
+          <t>Östsluttning mot myr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133698192</v>
+        <v>133697616</v>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>96780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,43 +1151,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>535</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuvetjärnen, Dls</t>
+          <t>SSO Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325432</v>
+        <v>325619</v>
       </c>
       <c r="R6" t="n">
-        <v>6557678</v>
+        <v>6557333</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,7 +1253,7 @@
         <v>133696761</v>
       </c>
       <c r="B7" t="n">
-        <v>96776</v>
+        <v>96783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,32 +1352,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133698174</v>
+        <v>133696898</v>
       </c>
       <c r="B8" t="n">
-        <v>97428</v>
+        <v>97810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,14 +1387,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kuvetjärnen, Dls</t>
+          <t>Norr Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325446</v>
+        <v>325388</v>
       </c>
       <c r="R8" t="n">
-        <v>6557657</v>
+        <v>6557926</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,17 +1447,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin  Sjöberg</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133696697</v>
+        <v>133697534</v>
       </c>
       <c r="B9" t="n">
-        <v>4776</v>
+        <v>97810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1426,43 +1465,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr Kuvetjärnen, Dls</t>
+          <t>SSO Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325411</v>
+        <v>325609</v>
       </c>
       <c r="R9" t="n">
-        <v>6557937</v>
+        <v>6557373</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,57 +1556,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133697616</v>
+        <v>133696982</v>
       </c>
       <c r="B10" t="n">
-        <v>96773</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>535</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SSO Kuvetjärnen, Dls</t>
+          <t>Sydost Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325619</v>
+        <v>325668</v>
       </c>
       <c r="R10" t="n">
-        <v>6557333</v>
+        <v>6557541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,49 +1665,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133696898</v>
+        <v>133697491</v>
       </c>
       <c r="B11" t="n">
-        <v>97803</v>
+        <v>75468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norr Kuvetjärnen, Dls</t>
+          <t>SSO Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325388</v>
+        <v>325565</v>
       </c>
       <c r="R11" t="n">
-        <v>6557926</v>
+        <v>6557419</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,53 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134287731</v>
+        <v>133698127</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>78776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kuvetjärnen, Dls</t>
+          <t>Söder Lilla Lekarvall, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325514</v>
+        <v>325663</v>
       </c>
       <c r="R12" t="n">
-        <v>6557642</v>
+        <v>6557566</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,12 +1834,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På hård kärnved av naturlig tallhögstubbe i exponerat läge.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,73 +1857,69 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134288280</v>
+        <v>133696697</v>
       </c>
       <c r="B13" t="n">
-        <v>97428</v>
+        <v>4776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söder om Kuvetjärnen, Dls</t>
+          <t>Norr Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325587</v>
+        <v>325411</v>
       </c>
       <c r="R13" t="n">
-        <v>6557366</v>
+        <v>6557937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,12 +1946,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1936,84 +1964,69 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134288382</v>
+        <v>133697670</v>
       </c>
       <c r="B14" t="n">
-        <v>97428</v>
+        <v>4776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr om Kuvetjärnen, Dls</t>
+          <t>Norr Skäktetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325377</v>
+        <v>325636</v>
       </c>
       <c r="R14" t="n">
-        <v>6557890</v>
+        <v>6557254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,12 +2053,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2058,38 +2071,880 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Låga med markkontakt # Picea abies</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133698197</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325432</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557678</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Roger Gran, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133696875</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norr Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>325375</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557928</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133697451</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SSO Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>325576</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557448</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133697666</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norr Skäktetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>325636</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557254</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133698192</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>325432</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6557678</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133697512</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SSO Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>325565</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6557419</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133697454</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SSO Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>325576</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6557448</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134287731</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>325514</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6557642</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Bård E. Andersen</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Bård E. Andersen</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133698174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134288280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134288382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697616</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696761</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696898</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697534</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696982</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1763,6 +1813,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697491</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133698127</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696697</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697670</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133698197</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696875</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697451</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697666</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2618,6 +2708,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133698192</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2727,6 +2822,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697512</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2834,6 +2934,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697454</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2945,8 +3050,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134287731</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>